--- a/artfynd/A 47930-2023 artfynd.xlsx
+++ b/artfynd/A 47930-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113680485</v>
       </c>
       <c r="B2" t="n">
-        <v>90690</v>
+        <v>90692</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47930-2023 artfynd.xlsx
+++ b/artfynd/A 47930-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113680485</v>
       </c>
       <c r="B2" t="n">
-        <v>90692</v>
+        <v>90693</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47930-2023 artfynd.xlsx
+++ b/artfynd/A 47930-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113680485</v>
       </c>
       <c r="B2" t="n">
-        <v>90693</v>
+        <v>90697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47930-2023 artfynd.xlsx
+++ b/artfynd/A 47930-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
